--- a/artfynd/A 31790-2021 artfynd.xlsx
+++ b/artfynd/A 31790-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129157323</v>
       </c>
       <c r="B2" t="n">
-        <v>98629</v>
+        <v>98634</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31790-2021 artfynd.xlsx
+++ b/artfynd/A 31790-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129157323</v>
       </c>
       <c r="B2" t="n">
-        <v>98634</v>
+        <v>98637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31790-2021 artfynd.xlsx
+++ b/artfynd/A 31790-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129157323</v>
       </c>
       <c r="B2" t="n">
-        <v>98637</v>
+        <v>98647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31790-2021 artfynd.xlsx
+++ b/artfynd/A 31790-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129157323</v>
       </c>
       <c r="B2" t="n">
-        <v>98647</v>
+        <v>98654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31790-2021 artfynd.xlsx
+++ b/artfynd/A 31790-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129157323</v>
       </c>
       <c r="B2" t="n">
-        <v>98654</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31790-2021 artfynd.xlsx
+++ b/artfynd/A 31790-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129157323</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31790-2021 artfynd.xlsx
+++ b/artfynd/A 31790-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129157323</v>
       </c>
       <c r="B2" t="n">
-        <v>98682</v>
+        <v>98683</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31790-2021 artfynd.xlsx
+++ b/artfynd/A 31790-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129157323</v>
       </c>
       <c r="B2" t="n">
-        <v>98683</v>
+        <v>98684</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31790-2021 artfynd.xlsx
+++ b/artfynd/A 31790-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129157323</v>
       </c>
       <c r="B2" t="n">
-        <v>98684</v>
+        <v>98688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31790-2021 artfynd.xlsx
+++ b/artfynd/A 31790-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129157323</v>
       </c>
       <c r="B2" t="n">
-        <v>98688</v>
+        <v>98690</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31790-2021 artfynd.xlsx
+++ b/artfynd/A 31790-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129157323</v>
       </c>
       <c r="B2" t="n">
-        <v>98690</v>
+        <v>98694</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31790-2021 artfynd.xlsx
+++ b/artfynd/A 31790-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129157323</v>
       </c>
       <c r="B2" t="n">
-        <v>98694</v>
+        <v>98702</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31790-2021 artfynd.xlsx
+++ b/artfynd/A 31790-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129157323</v>
       </c>
       <c r="B2" t="n">
-        <v>98702</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31790-2021 artfynd.xlsx
+++ b/artfynd/A 31790-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129157323</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31790-2021 artfynd.xlsx
+++ b/artfynd/A 31790-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129157323</v>
       </c>
       <c r="B2" t="n">
-        <v>98734</v>
+        <v>99096</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
